--- a/FM-MN-07_BAND SAW-02.xlsx
+++ b/FM-MN-07_BAND SAW-02.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30514"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From Iso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738FAAE1-12F4-4515-96CB-A086202D0C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBBC4D9-0437-4426-B976-A12DEB6DE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
   <sheets>
     <sheet name="BAND SAW-2" sheetId="7" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BAND SAW-2'!$A$1:$AG$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -77,7 +80,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -85,7 +88,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -109,7 +112,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -350,9 +353,6 @@
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,12 +402,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -429,17 +438,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -512,7 +515,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4654554</xdr:colOff>
+      <xdr:colOff>4092579</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>151341</xdr:rowOff>
     </xdr:to>
@@ -555,9 +558,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -595,7 +598,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -701,7 +704,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -843,7 +846,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -857,1123 +860,1123 @@
   <dimension ref="A1:AG19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="4.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="61.375" style="1" customWidth="1"/>
-    <col min="3" max="33" width="3.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" style="1" customWidth="1"/>
+    <col min="3" max="33" width="3.7109375" style="1" customWidth="1"/>
     <col min="34" max="245" width="9" style="1"/>
     <col min="246" max="246" width="7" style="1" customWidth="1"/>
-    <col min="247" max="247" width="14.75" style="1" customWidth="1"/>
-    <col min="248" max="248" width="13.375" style="1" customWidth="1"/>
-    <col min="249" max="252" width="9.875" style="1" customWidth="1"/>
-    <col min="253" max="253" width="10.75" style="1" customWidth="1"/>
-    <col min="254" max="255" width="9.875" style="1" customWidth="1"/>
-    <col min="256" max="256" width="14.875" style="1" customWidth="1"/>
-    <col min="257" max="257" width="23.875" style="1" customWidth="1"/>
-    <col min="258" max="258" width="13.25" style="1" customWidth="1"/>
+    <col min="247" max="247" width="14.7109375" style="1" customWidth="1"/>
+    <col min="248" max="248" width="13.42578125" style="1" customWidth="1"/>
+    <col min="249" max="252" width="9.85546875" style="1" customWidth="1"/>
+    <col min="253" max="253" width="10.7109375" style="1" customWidth="1"/>
+    <col min="254" max="255" width="9.85546875" style="1" customWidth="1"/>
+    <col min="256" max="256" width="14.85546875" style="1" customWidth="1"/>
+    <col min="257" max="257" width="23.85546875" style="1" customWidth="1"/>
+    <col min="258" max="258" width="13.28515625" style="1" customWidth="1"/>
     <col min="259" max="501" width="9" style="1"/>
     <col min="502" max="502" width="7" style="1" customWidth="1"/>
-    <col min="503" max="503" width="14.75" style="1" customWidth="1"/>
-    <col min="504" max="504" width="13.375" style="1" customWidth="1"/>
-    <col min="505" max="508" width="9.875" style="1" customWidth="1"/>
-    <col min="509" max="509" width="10.75" style="1" customWidth="1"/>
-    <col min="510" max="511" width="9.875" style="1" customWidth="1"/>
-    <col min="512" max="512" width="14.875" style="1" customWidth="1"/>
-    <col min="513" max="513" width="23.875" style="1" customWidth="1"/>
-    <col min="514" max="514" width="13.25" style="1" customWidth="1"/>
+    <col min="503" max="503" width="14.7109375" style="1" customWidth="1"/>
+    <col min="504" max="504" width="13.42578125" style="1" customWidth="1"/>
+    <col min="505" max="508" width="9.85546875" style="1" customWidth="1"/>
+    <col min="509" max="509" width="10.7109375" style="1" customWidth="1"/>
+    <col min="510" max="511" width="9.85546875" style="1" customWidth="1"/>
+    <col min="512" max="512" width="14.85546875" style="1" customWidth="1"/>
+    <col min="513" max="513" width="23.85546875" style="1" customWidth="1"/>
+    <col min="514" max="514" width="13.28515625" style="1" customWidth="1"/>
     <col min="515" max="757" width="9" style="1"/>
     <col min="758" max="758" width="7" style="1" customWidth="1"/>
-    <col min="759" max="759" width="14.75" style="1" customWidth="1"/>
-    <col min="760" max="760" width="13.375" style="1" customWidth="1"/>
-    <col min="761" max="764" width="9.875" style="1" customWidth="1"/>
-    <col min="765" max="765" width="10.75" style="1" customWidth="1"/>
-    <col min="766" max="767" width="9.875" style="1" customWidth="1"/>
-    <col min="768" max="768" width="14.875" style="1" customWidth="1"/>
-    <col min="769" max="769" width="23.875" style="1" customWidth="1"/>
-    <col min="770" max="770" width="13.25" style="1" customWidth="1"/>
+    <col min="759" max="759" width="14.7109375" style="1" customWidth="1"/>
+    <col min="760" max="760" width="13.42578125" style="1" customWidth="1"/>
+    <col min="761" max="764" width="9.85546875" style="1" customWidth="1"/>
+    <col min="765" max="765" width="10.7109375" style="1" customWidth="1"/>
+    <col min="766" max="767" width="9.85546875" style="1" customWidth="1"/>
+    <col min="768" max="768" width="14.85546875" style="1" customWidth="1"/>
+    <col min="769" max="769" width="23.85546875" style="1" customWidth="1"/>
+    <col min="770" max="770" width="13.28515625" style="1" customWidth="1"/>
     <col min="771" max="1013" width="9" style="1"/>
     <col min="1014" max="1014" width="7" style="1" customWidth="1"/>
-    <col min="1015" max="1015" width="14.75" style="1" customWidth="1"/>
-    <col min="1016" max="1016" width="13.375" style="1" customWidth="1"/>
-    <col min="1017" max="1020" width="9.875" style="1" customWidth="1"/>
-    <col min="1021" max="1021" width="10.75" style="1" customWidth="1"/>
-    <col min="1022" max="1023" width="9.875" style="1" customWidth="1"/>
-    <col min="1024" max="1024" width="14.875" style="1" customWidth="1"/>
-    <col min="1025" max="1025" width="23.875" style="1" customWidth="1"/>
-    <col min="1026" max="1026" width="13.25" style="1" customWidth="1"/>
+    <col min="1015" max="1015" width="14.7109375" style="1" customWidth="1"/>
+    <col min="1016" max="1016" width="13.42578125" style="1" customWidth="1"/>
+    <col min="1017" max="1020" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1021" max="1021" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1022" max="1023" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1024" max="1024" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1025" max="1025" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1026" max="1026" width="13.28515625" style="1" customWidth="1"/>
     <col min="1027" max="1269" width="9" style="1"/>
     <col min="1270" max="1270" width="7" style="1" customWidth="1"/>
-    <col min="1271" max="1271" width="14.75" style="1" customWidth="1"/>
-    <col min="1272" max="1272" width="13.375" style="1" customWidth="1"/>
-    <col min="1273" max="1276" width="9.875" style="1" customWidth="1"/>
-    <col min="1277" max="1277" width="10.75" style="1" customWidth="1"/>
-    <col min="1278" max="1279" width="9.875" style="1" customWidth="1"/>
-    <col min="1280" max="1280" width="14.875" style="1" customWidth="1"/>
-    <col min="1281" max="1281" width="23.875" style="1" customWidth="1"/>
-    <col min="1282" max="1282" width="13.25" style="1" customWidth="1"/>
+    <col min="1271" max="1271" width="14.7109375" style="1" customWidth="1"/>
+    <col min="1272" max="1272" width="13.42578125" style="1" customWidth="1"/>
+    <col min="1273" max="1276" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1277" max="1277" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1278" max="1279" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1280" max="1280" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1281" max="1281" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1282" max="1282" width="13.28515625" style="1" customWidth="1"/>
     <col min="1283" max="1525" width="9" style="1"/>
     <col min="1526" max="1526" width="7" style="1" customWidth="1"/>
-    <col min="1527" max="1527" width="14.75" style="1" customWidth="1"/>
-    <col min="1528" max="1528" width="13.375" style="1" customWidth="1"/>
-    <col min="1529" max="1532" width="9.875" style="1" customWidth="1"/>
-    <col min="1533" max="1533" width="10.75" style="1" customWidth="1"/>
-    <col min="1534" max="1535" width="9.875" style="1" customWidth="1"/>
-    <col min="1536" max="1536" width="14.875" style="1" customWidth="1"/>
-    <col min="1537" max="1537" width="23.875" style="1" customWidth="1"/>
-    <col min="1538" max="1538" width="13.25" style="1" customWidth="1"/>
+    <col min="1527" max="1527" width="14.7109375" style="1" customWidth="1"/>
+    <col min="1528" max="1528" width="13.42578125" style="1" customWidth="1"/>
+    <col min="1529" max="1532" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1533" max="1533" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1534" max="1535" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1536" max="1536" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1537" max="1537" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1538" max="1538" width="13.28515625" style="1" customWidth="1"/>
     <col min="1539" max="1781" width="9" style="1"/>
     <col min="1782" max="1782" width="7" style="1" customWidth="1"/>
-    <col min="1783" max="1783" width="14.75" style="1" customWidth="1"/>
-    <col min="1784" max="1784" width="13.375" style="1" customWidth="1"/>
-    <col min="1785" max="1788" width="9.875" style="1" customWidth="1"/>
-    <col min="1789" max="1789" width="10.75" style="1" customWidth="1"/>
-    <col min="1790" max="1791" width="9.875" style="1" customWidth="1"/>
-    <col min="1792" max="1792" width="14.875" style="1" customWidth="1"/>
-    <col min="1793" max="1793" width="23.875" style="1" customWidth="1"/>
-    <col min="1794" max="1794" width="13.25" style="1" customWidth="1"/>
+    <col min="1783" max="1783" width="14.7109375" style="1" customWidth="1"/>
+    <col min="1784" max="1784" width="13.42578125" style="1" customWidth="1"/>
+    <col min="1785" max="1788" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1789" max="1789" width="10.7109375" style="1" customWidth="1"/>
+    <col min="1790" max="1791" width="9.85546875" style="1" customWidth="1"/>
+    <col min="1792" max="1792" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1793" max="1793" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1794" max="1794" width="13.28515625" style="1" customWidth="1"/>
     <col min="1795" max="2037" width="9" style="1"/>
     <col min="2038" max="2038" width="7" style="1" customWidth="1"/>
-    <col min="2039" max="2039" width="14.75" style="1" customWidth="1"/>
-    <col min="2040" max="2040" width="13.375" style="1" customWidth="1"/>
-    <col min="2041" max="2044" width="9.875" style="1" customWidth="1"/>
-    <col min="2045" max="2045" width="10.75" style="1" customWidth="1"/>
-    <col min="2046" max="2047" width="9.875" style="1" customWidth="1"/>
-    <col min="2048" max="2048" width="14.875" style="1" customWidth="1"/>
-    <col min="2049" max="2049" width="23.875" style="1" customWidth="1"/>
-    <col min="2050" max="2050" width="13.25" style="1" customWidth="1"/>
+    <col min="2039" max="2039" width="14.7109375" style="1" customWidth="1"/>
+    <col min="2040" max="2040" width="13.42578125" style="1" customWidth="1"/>
+    <col min="2041" max="2044" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2045" max="2045" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2046" max="2047" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2048" max="2048" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2049" max="2049" width="23.85546875" style="1" customWidth="1"/>
+    <col min="2050" max="2050" width="13.28515625" style="1" customWidth="1"/>
     <col min="2051" max="2293" width="9" style="1"/>
     <col min="2294" max="2294" width="7" style="1" customWidth="1"/>
-    <col min="2295" max="2295" width="14.75" style="1" customWidth="1"/>
-    <col min="2296" max="2296" width="13.375" style="1" customWidth="1"/>
-    <col min="2297" max="2300" width="9.875" style="1" customWidth="1"/>
-    <col min="2301" max="2301" width="10.75" style="1" customWidth="1"/>
-    <col min="2302" max="2303" width="9.875" style="1" customWidth="1"/>
-    <col min="2304" max="2304" width="14.875" style="1" customWidth="1"/>
-    <col min="2305" max="2305" width="23.875" style="1" customWidth="1"/>
-    <col min="2306" max="2306" width="13.25" style="1" customWidth="1"/>
+    <col min="2295" max="2295" width="14.7109375" style="1" customWidth="1"/>
+    <col min="2296" max="2296" width="13.42578125" style="1" customWidth="1"/>
+    <col min="2297" max="2300" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2301" max="2301" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2302" max="2303" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2304" max="2304" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2305" max="2305" width="23.85546875" style="1" customWidth="1"/>
+    <col min="2306" max="2306" width="13.28515625" style="1" customWidth="1"/>
     <col min="2307" max="2549" width="9" style="1"/>
     <col min="2550" max="2550" width="7" style="1" customWidth="1"/>
-    <col min="2551" max="2551" width="14.75" style="1" customWidth="1"/>
-    <col min="2552" max="2552" width="13.375" style="1" customWidth="1"/>
-    <col min="2553" max="2556" width="9.875" style="1" customWidth="1"/>
-    <col min="2557" max="2557" width="10.75" style="1" customWidth="1"/>
-    <col min="2558" max="2559" width="9.875" style="1" customWidth="1"/>
-    <col min="2560" max="2560" width="14.875" style="1" customWidth="1"/>
-    <col min="2561" max="2561" width="23.875" style="1" customWidth="1"/>
-    <col min="2562" max="2562" width="13.25" style="1" customWidth="1"/>
+    <col min="2551" max="2551" width="14.7109375" style="1" customWidth="1"/>
+    <col min="2552" max="2552" width="13.42578125" style="1" customWidth="1"/>
+    <col min="2553" max="2556" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2557" max="2557" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2558" max="2559" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2560" max="2560" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2561" max="2561" width="23.85546875" style="1" customWidth="1"/>
+    <col min="2562" max="2562" width="13.28515625" style="1" customWidth="1"/>
     <col min="2563" max="2805" width="9" style="1"/>
     <col min="2806" max="2806" width="7" style="1" customWidth="1"/>
-    <col min="2807" max="2807" width="14.75" style="1" customWidth="1"/>
-    <col min="2808" max="2808" width="13.375" style="1" customWidth="1"/>
-    <col min="2809" max="2812" width="9.875" style="1" customWidth="1"/>
-    <col min="2813" max="2813" width="10.75" style="1" customWidth="1"/>
-    <col min="2814" max="2815" width="9.875" style="1" customWidth="1"/>
-    <col min="2816" max="2816" width="14.875" style="1" customWidth="1"/>
-    <col min="2817" max="2817" width="23.875" style="1" customWidth="1"/>
-    <col min="2818" max="2818" width="13.25" style="1" customWidth="1"/>
+    <col min="2807" max="2807" width="14.7109375" style="1" customWidth="1"/>
+    <col min="2808" max="2808" width="13.42578125" style="1" customWidth="1"/>
+    <col min="2809" max="2812" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2813" max="2813" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2814" max="2815" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2816" max="2816" width="14.85546875" style="1" customWidth="1"/>
+    <col min="2817" max="2817" width="23.85546875" style="1" customWidth="1"/>
+    <col min="2818" max="2818" width="13.28515625" style="1" customWidth="1"/>
     <col min="2819" max="3061" width="9" style="1"/>
     <col min="3062" max="3062" width="7" style="1" customWidth="1"/>
-    <col min="3063" max="3063" width="14.75" style="1" customWidth="1"/>
-    <col min="3064" max="3064" width="13.375" style="1" customWidth="1"/>
-    <col min="3065" max="3068" width="9.875" style="1" customWidth="1"/>
-    <col min="3069" max="3069" width="10.75" style="1" customWidth="1"/>
-    <col min="3070" max="3071" width="9.875" style="1" customWidth="1"/>
-    <col min="3072" max="3072" width="14.875" style="1" customWidth="1"/>
-    <col min="3073" max="3073" width="23.875" style="1" customWidth="1"/>
-    <col min="3074" max="3074" width="13.25" style="1" customWidth="1"/>
+    <col min="3063" max="3063" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3064" max="3064" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3065" max="3068" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3069" max="3069" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3070" max="3071" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3072" max="3072" width="14.85546875" style="1" customWidth="1"/>
+    <col min="3073" max="3073" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3074" max="3074" width="13.28515625" style="1" customWidth="1"/>
     <col min="3075" max="3317" width="9" style="1"/>
     <col min="3318" max="3318" width="7" style="1" customWidth="1"/>
-    <col min="3319" max="3319" width="14.75" style="1" customWidth="1"/>
-    <col min="3320" max="3320" width="13.375" style="1" customWidth="1"/>
-    <col min="3321" max="3324" width="9.875" style="1" customWidth="1"/>
-    <col min="3325" max="3325" width="10.75" style="1" customWidth="1"/>
-    <col min="3326" max="3327" width="9.875" style="1" customWidth="1"/>
-    <col min="3328" max="3328" width="14.875" style="1" customWidth="1"/>
-    <col min="3329" max="3329" width="23.875" style="1" customWidth="1"/>
-    <col min="3330" max="3330" width="13.25" style="1" customWidth="1"/>
+    <col min="3319" max="3319" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3320" max="3320" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3321" max="3324" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3325" max="3325" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3326" max="3327" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3328" max="3328" width="14.85546875" style="1" customWidth="1"/>
+    <col min="3329" max="3329" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3330" max="3330" width="13.28515625" style="1" customWidth="1"/>
     <col min="3331" max="3573" width="9" style="1"/>
     <col min="3574" max="3574" width="7" style="1" customWidth="1"/>
-    <col min="3575" max="3575" width="14.75" style="1" customWidth="1"/>
-    <col min="3576" max="3576" width="13.375" style="1" customWidth="1"/>
-    <col min="3577" max="3580" width="9.875" style="1" customWidth="1"/>
-    <col min="3581" max="3581" width="10.75" style="1" customWidth="1"/>
-    <col min="3582" max="3583" width="9.875" style="1" customWidth="1"/>
-    <col min="3584" max="3584" width="14.875" style="1" customWidth="1"/>
-    <col min="3585" max="3585" width="23.875" style="1" customWidth="1"/>
-    <col min="3586" max="3586" width="13.25" style="1" customWidth="1"/>
+    <col min="3575" max="3575" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3576" max="3576" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3577" max="3580" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3581" max="3581" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3582" max="3583" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3584" max="3584" width="14.85546875" style="1" customWidth="1"/>
+    <col min="3585" max="3585" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3586" max="3586" width="13.28515625" style="1" customWidth="1"/>
     <col min="3587" max="3829" width="9" style="1"/>
     <col min="3830" max="3830" width="7" style="1" customWidth="1"/>
-    <col min="3831" max="3831" width="14.75" style="1" customWidth="1"/>
-    <col min="3832" max="3832" width="13.375" style="1" customWidth="1"/>
-    <col min="3833" max="3836" width="9.875" style="1" customWidth="1"/>
-    <col min="3837" max="3837" width="10.75" style="1" customWidth="1"/>
-    <col min="3838" max="3839" width="9.875" style="1" customWidth="1"/>
-    <col min="3840" max="3840" width="14.875" style="1" customWidth="1"/>
-    <col min="3841" max="3841" width="23.875" style="1" customWidth="1"/>
-    <col min="3842" max="3842" width="13.25" style="1" customWidth="1"/>
+    <col min="3831" max="3831" width="14.7109375" style="1" customWidth="1"/>
+    <col min="3832" max="3832" width="13.42578125" style="1" customWidth="1"/>
+    <col min="3833" max="3836" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3837" max="3837" width="10.7109375" style="1" customWidth="1"/>
+    <col min="3838" max="3839" width="9.85546875" style="1" customWidth="1"/>
+    <col min="3840" max="3840" width="14.85546875" style="1" customWidth="1"/>
+    <col min="3841" max="3841" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3842" max="3842" width="13.28515625" style="1" customWidth="1"/>
     <col min="3843" max="4085" width="9" style="1"/>
     <col min="4086" max="4086" width="7" style="1" customWidth="1"/>
-    <col min="4087" max="4087" width="14.75" style="1" customWidth="1"/>
-    <col min="4088" max="4088" width="13.375" style="1" customWidth="1"/>
-    <col min="4089" max="4092" width="9.875" style="1" customWidth="1"/>
-    <col min="4093" max="4093" width="10.75" style="1" customWidth="1"/>
-    <col min="4094" max="4095" width="9.875" style="1" customWidth="1"/>
-    <col min="4096" max="4096" width="14.875" style="1" customWidth="1"/>
-    <col min="4097" max="4097" width="23.875" style="1" customWidth="1"/>
-    <col min="4098" max="4098" width="13.25" style="1" customWidth="1"/>
+    <col min="4087" max="4087" width="14.7109375" style="1" customWidth="1"/>
+    <col min="4088" max="4088" width="13.42578125" style="1" customWidth="1"/>
+    <col min="4089" max="4092" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4093" max="4093" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4094" max="4095" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4096" max="4096" width="14.85546875" style="1" customWidth="1"/>
+    <col min="4097" max="4097" width="23.85546875" style="1" customWidth="1"/>
+    <col min="4098" max="4098" width="13.28515625" style="1" customWidth="1"/>
     <col min="4099" max="4341" width="9" style="1"/>
     <col min="4342" max="4342" width="7" style="1" customWidth="1"/>
-    <col min="4343" max="4343" width="14.75" style="1" customWidth="1"/>
-    <col min="4344" max="4344" width="13.375" style="1" customWidth="1"/>
-    <col min="4345" max="4348" width="9.875" style="1" customWidth="1"/>
-    <col min="4349" max="4349" width="10.75" style="1" customWidth="1"/>
-    <col min="4350" max="4351" width="9.875" style="1" customWidth="1"/>
-    <col min="4352" max="4352" width="14.875" style="1" customWidth="1"/>
-    <col min="4353" max="4353" width="23.875" style="1" customWidth="1"/>
-    <col min="4354" max="4354" width="13.25" style="1" customWidth="1"/>
+    <col min="4343" max="4343" width="14.7109375" style="1" customWidth="1"/>
+    <col min="4344" max="4344" width="13.42578125" style="1" customWidth="1"/>
+    <col min="4345" max="4348" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4349" max="4349" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4350" max="4351" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4352" max="4352" width="14.85546875" style="1" customWidth="1"/>
+    <col min="4353" max="4353" width="23.85546875" style="1" customWidth="1"/>
+    <col min="4354" max="4354" width="13.28515625" style="1" customWidth="1"/>
     <col min="4355" max="4597" width="9" style="1"/>
     <col min="4598" max="4598" width="7" style="1" customWidth="1"/>
-    <col min="4599" max="4599" width="14.75" style="1" customWidth="1"/>
-    <col min="4600" max="4600" width="13.375" style="1" customWidth="1"/>
-    <col min="4601" max="4604" width="9.875" style="1" customWidth="1"/>
-    <col min="4605" max="4605" width="10.75" style="1" customWidth="1"/>
-    <col min="4606" max="4607" width="9.875" style="1" customWidth="1"/>
-    <col min="4608" max="4608" width="14.875" style="1" customWidth="1"/>
-    <col min="4609" max="4609" width="23.875" style="1" customWidth="1"/>
-    <col min="4610" max="4610" width="13.25" style="1" customWidth="1"/>
+    <col min="4599" max="4599" width="14.7109375" style="1" customWidth="1"/>
+    <col min="4600" max="4600" width="13.42578125" style="1" customWidth="1"/>
+    <col min="4601" max="4604" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4605" max="4605" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4606" max="4607" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4608" max="4608" width="14.85546875" style="1" customWidth="1"/>
+    <col min="4609" max="4609" width="23.85546875" style="1" customWidth="1"/>
+    <col min="4610" max="4610" width="13.28515625" style="1" customWidth="1"/>
     <col min="4611" max="4853" width="9" style="1"/>
     <col min="4854" max="4854" width="7" style="1" customWidth="1"/>
-    <col min="4855" max="4855" width="14.75" style="1" customWidth="1"/>
-    <col min="4856" max="4856" width="13.375" style="1" customWidth="1"/>
-    <col min="4857" max="4860" width="9.875" style="1" customWidth="1"/>
-    <col min="4861" max="4861" width="10.75" style="1" customWidth="1"/>
-    <col min="4862" max="4863" width="9.875" style="1" customWidth="1"/>
-    <col min="4864" max="4864" width="14.875" style="1" customWidth="1"/>
-    <col min="4865" max="4865" width="23.875" style="1" customWidth="1"/>
-    <col min="4866" max="4866" width="13.25" style="1" customWidth="1"/>
+    <col min="4855" max="4855" width="14.7109375" style="1" customWidth="1"/>
+    <col min="4856" max="4856" width="13.42578125" style="1" customWidth="1"/>
+    <col min="4857" max="4860" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4861" max="4861" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4862" max="4863" width="9.85546875" style="1" customWidth="1"/>
+    <col min="4864" max="4864" width="14.85546875" style="1" customWidth="1"/>
+    <col min="4865" max="4865" width="23.85546875" style="1" customWidth="1"/>
+    <col min="4866" max="4866" width="13.28515625" style="1" customWidth="1"/>
     <col min="4867" max="5109" width="9" style="1"/>
     <col min="5110" max="5110" width="7" style="1" customWidth="1"/>
-    <col min="5111" max="5111" width="14.75" style="1" customWidth="1"/>
-    <col min="5112" max="5112" width="13.375" style="1" customWidth="1"/>
-    <col min="5113" max="5116" width="9.875" style="1" customWidth="1"/>
-    <col min="5117" max="5117" width="10.75" style="1" customWidth="1"/>
-    <col min="5118" max="5119" width="9.875" style="1" customWidth="1"/>
-    <col min="5120" max="5120" width="14.875" style="1" customWidth="1"/>
-    <col min="5121" max="5121" width="23.875" style="1" customWidth="1"/>
-    <col min="5122" max="5122" width="13.25" style="1" customWidth="1"/>
+    <col min="5111" max="5111" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5112" max="5112" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5113" max="5116" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5117" max="5117" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5118" max="5119" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5120" max="5120" width="14.85546875" style="1" customWidth="1"/>
+    <col min="5121" max="5121" width="23.85546875" style="1" customWidth="1"/>
+    <col min="5122" max="5122" width="13.28515625" style="1" customWidth="1"/>
     <col min="5123" max="5365" width="9" style="1"/>
     <col min="5366" max="5366" width="7" style="1" customWidth="1"/>
-    <col min="5367" max="5367" width="14.75" style="1" customWidth="1"/>
-    <col min="5368" max="5368" width="13.375" style="1" customWidth="1"/>
-    <col min="5369" max="5372" width="9.875" style="1" customWidth="1"/>
-    <col min="5373" max="5373" width="10.75" style="1" customWidth="1"/>
-    <col min="5374" max="5375" width="9.875" style="1" customWidth="1"/>
-    <col min="5376" max="5376" width="14.875" style="1" customWidth="1"/>
-    <col min="5377" max="5377" width="23.875" style="1" customWidth="1"/>
-    <col min="5378" max="5378" width="13.25" style="1" customWidth="1"/>
+    <col min="5367" max="5367" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5368" max="5368" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5369" max="5372" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5373" max="5373" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5374" max="5375" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5376" max="5376" width="14.85546875" style="1" customWidth="1"/>
+    <col min="5377" max="5377" width="23.85546875" style="1" customWidth="1"/>
+    <col min="5378" max="5378" width="13.28515625" style="1" customWidth="1"/>
     <col min="5379" max="5621" width="9" style="1"/>
     <col min="5622" max="5622" width="7" style="1" customWidth="1"/>
-    <col min="5623" max="5623" width="14.75" style="1" customWidth="1"/>
-    <col min="5624" max="5624" width="13.375" style="1" customWidth="1"/>
-    <col min="5625" max="5628" width="9.875" style="1" customWidth="1"/>
-    <col min="5629" max="5629" width="10.75" style="1" customWidth="1"/>
-    <col min="5630" max="5631" width="9.875" style="1" customWidth="1"/>
-    <col min="5632" max="5632" width="14.875" style="1" customWidth="1"/>
-    <col min="5633" max="5633" width="23.875" style="1" customWidth="1"/>
-    <col min="5634" max="5634" width="13.25" style="1" customWidth="1"/>
+    <col min="5623" max="5623" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5624" max="5624" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5625" max="5628" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5629" max="5629" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5630" max="5631" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5632" max="5632" width="14.85546875" style="1" customWidth="1"/>
+    <col min="5633" max="5633" width="23.85546875" style="1" customWidth="1"/>
+    <col min="5634" max="5634" width="13.28515625" style="1" customWidth="1"/>
     <col min="5635" max="5877" width="9" style="1"/>
     <col min="5878" max="5878" width="7" style="1" customWidth="1"/>
-    <col min="5879" max="5879" width="14.75" style="1" customWidth="1"/>
-    <col min="5880" max="5880" width="13.375" style="1" customWidth="1"/>
-    <col min="5881" max="5884" width="9.875" style="1" customWidth="1"/>
-    <col min="5885" max="5885" width="10.75" style="1" customWidth="1"/>
-    <col min="5886" max="5887" width="9.875" style="1" customWidth="1"/>
-    <col min="5888" max="5888" width="14.875" style="1" customWidth="1"/>
-    <col min="5889" max="5889" width="23.875" style="1" customWidth="1"/>
-    <col min="5890" max="5890" width="13.25" style="1" customWidth="1"/>
+    <col min="5879" max="5879" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5880" max="5880" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5881" max="5884" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5885" max="5885" width="10.7109375" style="1" customWidth="1"/>
+    <col min="5886" max="5887" width="9.85546875" style="1" customWidth="1"/>
+    <col min="5888" max="5888" width="14.85546875" style="1" customWidth="1"/>
+    <col min="5889" max="5889" width="23.85546875" style="1" customWidth="1"/>
+    <col min="5890" max="5890" width="13.28515625" style="1" customWidth="1"/>
     <col min="5891" max="6133" width="9" style="1"/>
     <col min="6134" max="6134" width="7" style="1" customWidth="1"/>
-    <col min="6135" max="6135" width="14.75" style="1" customWidth="1"/>
-    <col min="6136" max="6136" width="13.375" style="1" customWidth="1"/>
-    <col min="6137" max="6140" width="9.875" style="1" customWidth="1"/>
-    <col min="6141" max="6141" width="10.75" style="1" customWidth="1"/>
-    <col min="6142" max="6143" width="9.875" style="1" customWidth="1"/>
-    <col min="6144" max="6144" width="14.875" style="1" customWidth="1"/>
-    <col min="6145" max="6145" width="23.875" style="1" customWidth="1"/>
-    <col min="6146" max="6146" width="13.25" style="1" customWidth="1"/>
+    <col min="6135" max="6135" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6136" max="6136" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6137" max="6140" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6141" max="6141" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6142" max="6143" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6144" max="6144" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6145" max="6145" width="23.85546875" style="1" customWidth="1"/>
+    <col min="6146" max="6146" width="13.28515625" style="1" customWidth="1"/>
     <col min="6147" max="6389" width="9" style="1"/>
     <col min="6390" max="6390" width="7" style="1" customWidth="1"/>
-    <col min="6391" max="6391" width="14.75" style="1" customWidth="1"/>
-    <col min="6392" max="6392" width="13.375" style="1" customWidth="1"/>
-    <col min="6393" max="6396" width="9.875" style="1" customWidth="1"/>
-    <col min="6397" max="6397" width="10.75" style="1" customWidth="1"/>
-    <col min="6398" max="6399" width="9.875" style="1" customWidth="1"/>
-    <col min="6400" max="6400" width="14.875" style="1" customWidth="1"/>
-    <col min="6401" max="6401" width="23.875" style="1" customWidth="1"/>
-    <col min="6402" max="6402" width="13.25" style="1" customWidth="1"/>
+    <col min="6391" max="6391" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6392" max="6392" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6393" max="6396" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6397" max="6397" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6398" max="6399" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6400" max="6400" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6401" max="6401" width="23.85546875" style="1" customWidth="1"/>
+    <col min="6402" max="6402" width="13.28515625" style="1" customWidth="1"/>
     <col min="6403" max="6645" width="9" style="1"/>
     <col min="6646" max="6646" width="7" style="1" customWidth="1"/>
-    <col min="6647" max="6647" width="14.75" style="1" customWidth="1"/>
-    <col min="6648" max="6648" width="13.375" style="1" customWidth="1"/>
-    <col min="6649" max="6652" width="9.875" style="1" customWidth="1"/>
-    <col min="6653" max="6653" width="10.75" style="1" customWidth="1"/>
-    <col min="6654" max="6655" width="9.875" style="1" customWidth="1"/>
-    <col min="6656" max="6656" width="14.875" style="1" customWidth="1"/>
-    <col min="6657" max="6657" width="23.875" style="1" customWidth="1"/>
-    <col min="6658" max="6658" width="13.25" style="1" customWidth="1"/>
+    <col min="6647" max="6647" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6648" max="6648" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6649" max="6652" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6653" max="6653" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6654" max="6655" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6656" max="6656" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6657" max="6657" width="23.85546875" style="1" customWidth="1"/>
+    <col min="6658" max="6658" width="13.28515625" style="1" customWidth="1"/>
     <col min="6659" max="6901" width="9" style="1"/>
     <col min="6902" max="6902" width="7" style="1" customWidth="1"/>
-    <col min="6903" max="6903" width="14.75" style="1" customWidth="1"/>
-    <col min="6904" max="6904" width="13.375" style="1" customWidth="1"/>
-    <col min="6905" max="6908" width="9.875" style="1" customWidth="1"/>
-    <col min="6909" max="6909" width="10.75" style="1" customWidth="1"/>
-    <col min="6910" max="6911" width="9.875" style="1" customWidth="1"/>
-    <col min="6912" max="6912" width="14.875" style="1" customWidth="1"/>
-    <col min="6913" max="6913" width="23.875" style="1" customWidth="1"/>
-    <col min="6914" max="6914" width="13.25" style="1" customWidth="1"/>
+    <col min="6903" max="6903" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6904" max="6904" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6905" max="6908" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6909" max="6909" width="10.7109375" style="1" customWidth="1"/>
+    <col min="6910" max="6911" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6912" max="6912" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6913" max="6913" width="23.85546875" style="1" customWidth="1"/>
+    <col min="6914" max="6914" width="13.28515625" style="1" customWidth="1"/>
     <col min="6915" max="7157" width="9" style="1"/>
     <col min="7158" max="7158" width="7" style="1" customWidth="1"/>
-    <col min="7159" max="7159" width="14.75" style="1" customWidth="1"/>
-    <col min="7160" max="7160" width="13.375" style="1" customWidth="1"/>
-    <col min="7161" max="7164" width="9.875" style="1" customWidth="1"/>
-    <col min="7165" max="7165" width="10.75" style="1" customWidth="1"/>
-    <col min="7166" max="7167" width="9.875" style="1" customWidth="1"/>
-    <col min="7168" max="7168" width="14.875" style="1" customWidth="1"/>
-    <col min="7169" max="7169" width="23.875" style="1" customWidth="1"/>
-    <col min="7170" max="7170" width="13.25" style="1" customWidth="1"/>
+    <col min="7159" max="7159" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7160" max="7160" width="13.42578125" style="1" customWidth="1"/>
+    <col min="7161" max="7164" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7165" max="7165" width="10.7109375" style="1" customWidth="1"/>
+    <col min="7166" max="7167" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7168" max="7168" width="14.85546875" style="1" customWidth="1"/>
+    <col min="7169" max="7169" width="23.85546875" style="1" customWidth="1"/>
+    <col min="7170" max="7170" width="13.28515625" style="1" customWidth="1"/>
     <col min="7171" max="7413" width="9" style="1"/>
     <col min="7414" max="7414" width="7" style="1" customWidth="1"/>
-    <col min="7415" max="7415" width="14.75" style="1" customWidth="1"/>
-    <col min="7416" max="7416" width="13.375" style="1" customWidth="1"/>
-    <col min="7417" max="7420" width="9.875" style="1" customWidth="1"/>
-    <col min="7421" max="7421" width="10.75" style="1" customWidth="1"/>
-    <col min="7422" max="7423" width="9.875" style="1" customWidth="1"/>
-    <col min="7424" max="7424" width="14.875" style="1" customWidth="1"/>
-    <col min="7425" max="7425" width="23.875" style="1" customWidth="1"/>
-    <col min="7426" max="7426" width="13.25" style="1" customWidth="1"/>
+    <col min="7415" max="7415" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7416" max="7416" width="13.42578125" style="1" customWidth="1"/>
+    <col min="7417" max="7420" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7421" max="7421" width="10.7109375" style="1" customWidth="1"/>
+    <col min="7422" max="7423" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7424" max="7424" width="14.85546875" style="1" customWidth="1"/>
+    <col min="7425" max="7425" width="23.85546875" style="1" customWidth="1"/>
+    <col min="7426" max="7426" width="13.28515625" style="1" customWidth="1"/>
     <col min="7427" max="7669" width="9" style="1"/>
     <col min="7670" max="7670" width="7" style="1" customWidth="1"/>
-    <col min="7671" max="7671" width="14.75" style="1" customWidth="1"/>
-    <col min="7672" max="7672" width="13.375" style="1" customWidth="1"/>
-    <col min="7673" max="7676" width="9.875" style="1" customWidth="1"/>
-    <col min="7677" max="7677" width="10.75" style="1" customWidth="1"/>
-    <col min="7678" max="7679" width="9.875" style="1" customWidth="1"/>
-    <col min="7680" max="7680" width="14.875" style="1" customWidth="1"/>
-    <col min="7681" max="7681" width="23.875" style="1" customWidth="1"/>
-    <col min="7682" max="7682" width="13.25" style="1" customWidth="1"/>
+    <col min="7671" max="7671" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7672" max="7672" width="13.42578125" style="1" customWidth="1"/>
+    <col min="7673" max="7676" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7677" max="7677" width="10.7109375" style="1" customWidth="1"/>
+    <col min="7678" max="7679" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7680" max="7680" width="14.85546875" style="1" customWidth="1"/>
+    <col min="7681" max="7681" width="23.85546875" style="1" customWidth="1"/>
+    <col min="7682" max="7682" width="13.28515625" style="1" customWidth="1"/>
     <col min="7683" max="7925" width="9" style="1"/>
     <col min="7926" max="7926" width="7" style="1" customWidth="1"/>
-    <col min="7927" max="7927" width="14.75" style="1" customWidth="1"/>
-    <col min="7928" max="7928" width="13.375" style="1" customWidth="1"/>
-    <col min="7929" max="7932" width="9.875" style="1" customWidth="1"/>
-    <col min="7933" max="7933" width="10.75" style="1" customWidth="1"/>
-    <col min="7934" max="7935" width="9.875" style="1" customWidth="1"/>
-    <col min="7936" max="7936" width="14.875" style="1" customWidth="1"/>
-    <col min="7937" max="7937" width="23.875" style="1" customWidth="1"/>
-    <col min="7938" max="7938" width="13.25" style="1" customWidth="1"/>
+    <col min="7927" max="7927" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7928" max="7928" width="13.42578125" style="1" customWidth="1"/>
+    <col min="7929" max="7932" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7933" max="7933" width="10.7109375" style="1" customWidth="1"/>
+    <col min="7934" max="7935" width="9.85546875" style="1" customWidth="1"/>
+    <col min="7936" max="7936" width="14.85546875" style="1" customWidth="1"/>
+    <col min="7937" max="7937" width="23.85546875" style="1" customWidth="1"/>
+    <col min="7938" max="7938" width="13.28515625" style="1" customWidth="1"/>
     <col min="7939" max="8181" width="9" style="1"/>
     <col min="8182" max="8182" width="7" style="1" customWidth="1"/>
-    <col min="8183" max="8183" width="14.75" style="1" customWidth="1"/>
-    <col min="8184" max="8184" width="13.375" style="1" customWidth="1"/>
-    <col min="8185" max="8188" width="9.875" style="1" customWidth="1"/>
-    <col min="8189" max="8189" width="10.75" style="1" customWidth="1"/>
-    <col min="8190" max="8191" width="9.875" style="1" customWidth="1"/>
-    <col min="8192" max="8192" width="14.875" style="1" customWidth="1"/>
-    <col min="8193" max="8193" width="23.875" style="1" customWidth="1"/>
-    <col min="8194" max="8194" width="13.25" style="1" customWidth="1"/>
+    <col min="8183" max="8183" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8184" max="8184" width="13.42578125" style="1" customWidth="1"/>
+    <col min="8185" max="8188" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8189" max="8189" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8190" max="8191" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8192" max="8192" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8193" max="8193" width="23.85546875" style="1" customWidth="1"/>
+    <col min="8194" max="8194" width="13.28515625" style="1" customWidth="1"/>
     <col min="8195" max="8437" width="9" style="1"/>
     <col min="8438" max="8438" width="7" style="1" customWidth="1"/>
-    <col min="8439" max="8439" width="14.75" style="1" customWidth="1"/>
-    <col min="8440" max="8440" width="13.375" style="1" customWidth="1"/>
-    <col min="8441" max="8444" width="9.875" style="1" customWidth="1"/>
-    <col min="8445" max="8445" width="10.75" style="1" customWidth="1"/>
-    <col min="8446" max="8447" width="9.875" style="1" customWidth="1"/>
-    <col min="8448" max="8448" width="14.875" style="1" customWidth="1"/>
-    <col min="8449" max="8449" width="23.875" style="1" customWidth="1"/>
-    <col min="8450" max="8450" width="13.25" style="1" customWidth="1"/>
+    <col min="8439" max="8439" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8440" max="8440" width="13.42578125" style="1" customWidth="1"/>
+    <col min="8441" max="8444" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8445" max="8445" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8446" max="8447" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8448" max="8448" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8449" max="8449" width="23.85546875" style="1" customWidth="1"/>
+    <col min="8450" max="8450" width="13.28515625" style="1" customWidth="1"/>
     <col min="8451" max="8693" width="9" style="1"/>
     <col min="8694" max="8694" width="7" style="1" customWidth="1"/>
-    <col min="8695" max="8695" width="14.75" style="1" customWidth="1"/>
-    <col min="8696" max="8696" width="13.375" style="1" customWidth="1"/>
-    <col min="8697" max="8700" width="9.875" style="1" customWidth="1"/>
-    <col min="8701" max="8701" width="10.75" style="1" customWidth="1"/>
-    <col min="8702" max="8703" width="9.875" style="1" customWidth="1"/>
-    <col min="8704" max="8704" width="14.875" style="1" customWidth="1"/>
-    <col min="8705" max="8705" width="23.875" style="1" customWidth="1"/>
-    <col min="8706" max="8706" width="13.25" style="1" customWidth="1"/>
+    <col min="8695" max="8695" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8696" max="8696" width="13.42578125" style="1" customWidth="1"/>
+    <col min="8697" max="8700" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8701" max="8701" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8702" max="8703" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8704" max="8704" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8705" max="8705" width="23.85546875" style="1" customWidth="1"/>
+    <col min="8706" max="8706" width="13.28515625" style="1" customWidth="1"/>
     <col min="8707" max="8949" width="9" style="1"/>
     <col min="8950" max="8950" width="7" style="1" customWidth="1"/>
-    <col min="8951" max="8951" width="14.75" style="1" customWidth="1"/>
-    <col min="8952" max="8952" width="13.375" style="1" customWidth="1"/>
-    <col min="8953" max="8956" width="9.875" style="1" customWidth="1"/>
-    <col min="8957" max="8957" width="10.75" style="1" customWidth="1"/>
-    <col min="8958" max="8959" width="9.875" style="1" customWidth="1"/>
-    <col min="8960" max="8960" width="14.875" style="1" customWidth="1"/>
-    <col min="8961" max="8961" width="23.875" style="1" customWidth="1"/>
-    <col min="8962" max="8962" width="13.25" style="1" customWidth="1"/>
+    <col min="8951" max="8951" width="14.7109375" style="1" customWidth="1"/>
+    <col min="8952" max="8952" width="13.42578125" style="1" customWidth="1"/>
+    <col min="8953" max="8956" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8957" max="8957" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8958" max="8959" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8960" max="8960" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8961" max="8961" width="23.85546875" style="1" customWidth="1"/>
+    <col min="8962" max="8962" width="13.28515625" style="1" customWidth="1"/>
     <col min="8963" max="9205" width="9" style="1"/>
     <col min="9206" max="9206" width="7" style="1" customWidth="1"/>
-    <col min="9207" max="9207" width="14.75" style="1" customWidth="1"/>
-    <col min="9208" max="9208" width="13.375" style="1" customWidth="1"/>
-    <col min="9209" max="9212" width="9.875" style="1" customWidth="1"/>
-    <col min="9213" max="9213" width="10.75" style="1" customWidth="1"/>
-    <col min="9214" max="9215" width="9.875" style="1" customWidth="1"/>
-    <col min="9216" max="9216" width="14.875" style="1" customWidth="1"/>
-    <col min="9217" max="9217" width="23.875" style="1" customWidth="1"/>
-    <col min="9218" max="9218" width="13.25" style="1" customWidth="1"/>
+    <col min="9207" max="9207" width="14.7109375" style="1" customWidth="1"/>
+    <col min="9208" max="9208" width="13.42578125" style="1" customWidth="1"/>
+    <col min="9209" max="9212" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9213" max="9213" width="10.7109375" style="1" customWidth="1"/>
+    <col min="9214" max="9215" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9216" max="9216" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9217" max="9217" width="23.85546875" style="1" customWidth="1"/>
+    <col min="9218" max="9218" width="13.28515625" style="1" customWidth="1"/>
     <col min="9219" max="9461" width="9" style="1"/>
     <col min="9462" max="9462" width="7" style="1" customWidth="1"/>
-    <col min="9463" max="9463" width="14.75" style="1" customWidth="1"/>
-    <col min="9464" max="9464" width="13.375" style="1" customWidth="1"/>
-    <col min="9465" max="9468" width="9.875" style="1" customWidth="1"/>
-    <col min="9469" max="9469" width="10.75" style="1" customWidth="1"/>
-    <col min="9470" max="9471" width="9.875" style="1" customWidth="1"/>
-    <col min="9472" max="9472" width="14.875" style="1" customWidth="1"/>
-    <col min="9473" max="9473" width="23.875" style="1" customWidth="1"/>
-    <col min="9474" max="9474" width="13.25" style="1" customWidth="1"/>
+    <col min="9463" max="9463" width="14.7109375" style="1" customWidth="1"/>
+    <col min="9464" max="9464" width="13.42578125" style="1" customWidth="1"/>
+    <col min="9465" max="9468" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9469" max="9469" width="10.7109375" style="1" customWidth="1"/>
+    <col min="9470" max="9471" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9472" max="9472" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9473" max="9473" width="23.85546875" style="1" customWidth="1"/>
+    <col min="9474" max="9474" width="13.28515625" style="1" customWidth="1"/>
     <col min="9475" max="9717" width="9" style="1"/>
     <col min="9718" max="9718" width="7" style="1" customWidth="1"/>
-    <col min="9719" max="9719" width="14.75" style="1" customWidth="1"/>
-    <col min="9720" max="9720" width="13.375" style="1" customWidth="1"/>
-    <col min="9721" max="9724" width="9.875" style="1" customWidth="1"/>
-    <col min="9725" max="9725" width="10.75" style="1" customWidth="1"/>
-    <col min="9726" max="9727" width="9.875" style="1" customWidth="1"/>
-    <col min="9728" max="9728" width="14.875" style="1" customWidth="1"/>
-    <col min="9729" max="9729" width="23.875" style="1" customWidth="1"/>
-    <col min="9730" max="9730" width="13.25" style="1" customWidth="1"/>
+    <col min="9719" max="9719" width="14.7109375" style="1" customWidth="1"/>
+    <col min="9720" max="9720" width="13.42578125" style="1" customWidth="1"/>
+    <col min="9721" max="9724" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9725" max="9725" width="10.7109375" style="1" customWidth="1"/>
+    <col min="9726" max="9727" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9728" max="9728" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9729" max="9729" width="23.85546875" style="1" customWidth="1"/>
+    <col min="9730" max="9730" width="13.28515625" style="1" customWidth="1"/>
     <col min="9731" max="9973" width="9" style="1"/>
     <col min="9974" max="9974" width="7" style="1" customWidth="1"/>
-    <col min="9975" max="9975" width="14.75" style="1" customWidth="1"/>
-    <col min="9976" max="9976" width="13.375" style="1" customWidth="1"/>
-    <col min="9977" max="9980" width="9.875" style="1" customWidth="1"/>
-    <col min="9981" max="9981" width="10.75" style="1" customWidth="1"/>
-    <col min="9982" max="9983" width="9.875" style="1" customWidth="1"/>
-    <col min="9984" max="9984" width="14.875" style="1" customWidth="1"/>
-    <col min="9985" max="9985" width="23.875" style="1" customWidth="1"/>
-    <col min="9986" max="9986" width="13.25" style="1" customWidth="1"/>
+    <col min="9975" max="9975" width="14.7109375" style="1" customWidth="1"/>
+    <col min="9976" max="9976" width="13.42578125" style="1" customWidth="1"/>
+    <col min="9977" max="9980" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9981" max="9981" width="10.7109375" style="1" customWidth="1"/>
+    <col min="9982" max="9983" width="9.85546875" style="1" customWidth="1"/>
+    <col min="9984" max="9984" width="14.85546875" style="1" customWidth="1"/>
+    <col min="9985" max="9985" width="23.85546875" style="1" customWidth="1"/>
+    <col min="9986" max="9986" width="13.28515625" style="1" customWidth="1"/>
     <col min="9987" max="10229" width="9" style="1"/>
     <col min="10230" max="10230" width="7" style="1" customWidth="1"/>
-    <col min="10231" max="10231" width="14.75" style="1" customWidth="1"/>
-    <col min="10232" max="10232" width="13.375" style="1" customWidth="1"/>
-    <col min="10233" max="10236" width="9.875" style="1" customWidth="1"/>
-    <col min="10237" max="10237" width="10.75" style="1" customWidth="1"/>
-    <col min="10238" max="10239" width="9.875" style="1" customWidth="1"/>
-    <col min="10240" max="10240" width="14.875" style="1" customWidth="1"/>
-    <col min="10241" max="10241" width="23.875" style="1" customWidth="1"/>
-    <col min="10242" max="10242" width="13.25" style="1" customWidth="1"/>
+    <col min="10231" max="10231" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10232" max="10232" width="13.42578125" style="1" customWidth="1"/>
+    <col min="10233" max="10236" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10237" max="10237" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10238" max="10239" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10240" max="10240" width="14.85546875" style="1" customWidth="1"/>
+    <col min="10241" max="10241" width="23.85546875" style="1" customWidth="1"/>
+    <col min="10242" max="10242" width="13.28515625" style="1" customWidth="1"/>
     <col min="10243" max="10485" width="9" style="1"/>
     <col min="10486" max="10486" width="7" style="1" customWidth="1"/>
-    <col min="10487" max="10487" width="14.75" style="1" customWidth="1"/>
-    <col min="10488" max="10488" width="13.375" style="1" customWidth="1"/>
-    <col min="10489" max="10492" width="9.875" style="1" customWidth="1"/>
-    <col min="10493" max="10493" width="10.75" style="1" customWidth="1"/>
-    <col min="10494" max="10495" width="9.875" style="1" customWidth="1"/>
-    <col min="10496" max="10496" width="14.875" style="1" customWidth="1"/>
-    <col min="10497" max="10497" width="23.875" style="1" customWidth="1"/>
-    <col min="10498" max="10498" width="13.25" style="1" customWidth="1"/>
+    <col min="10487" max="10487" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10488" max="10488" width="13.42578125" style="1" customWidth="1"/>
+    <col min="10489" max="10492" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10493" max="10493" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10494" max="10495" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10496" max="10496" width="14.85546875" style="1" customWidth="1"/>
+    <col min="10497" max="10497" width="23.85546875" style="1" customWidth="1"/>
+    <col min="10498" max="10498" width="13.28515625" style="1" customWidth="1"/>
     <col min="10499" max="10741" width="9" style="1"/>
     <col min="10742" max="10742" width="7" style="1" customWidth="1"/>
-    <col min="10743" max="10743" width="14.75" style="1" customWidth="1"/>
-    <col min="10744" max="10744" width="13.375" style="1" customWidth="1"/>
-    <col min="10745" max="10748" width="9.875" style="1" customWidth="1"/>
-    <col min="10749" max="10749" width="10.75" style="1" customWidth="1"/>
-    <col min="10750" max="10751" width="9.875" style="1" customWidth="1"/>
-    <col min="10752" max="10752" width="14.875" style="1" customWidth="1"/>
-    <col min="10753" max="10753" width="23.875" style="1" customWidth="1"/>
-    <col min="10754" max="10754" width="13.25" style="1" customWidth="1"/>
+    <col min="10743" max="10743" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10744" max="10744" width="13.42578125" style="1" customWidth="1"/>
+    <col min="10745" max="10748" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10749" max="10749" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10750" max="10751" width="9.85546875" style="1" customWidth="1"/>
+    <col min="10752" max="10752" width="14.85546875" style="1" customWidth="1"/>
+    <col min="10753" max="10753" width="23.85546875" style="1" customWidth="1"/>
+    <col min="10754" max="10754" width="13.28515625" style="1" customWidth="1"/>
     <col min="10755" max="10997" width="9" style="1"/>
     <col min="10998" max="10998" width="7" style="1" customWidth="1"/>
-    <col min="10999" max="10999" width="14.75" style="1" customWidth="1"/>
-    <col min="11000" max="11000" width="13.375" style="1" customWidth="1"/>
-    <col min="11001" max="11004" width="9.875" style="1" customWidth="1"/>
-    <col min="11005" max="11005" width="10.75" style="1" customWidth="1"/>
-    <col min="11006" max="11007" width="9.875" style="1" customWidth="1"/>
-    <col min="11008" max="11008" width="14.875" style="1" customWidth="1"/>
-    <col min="11009" max="11009" width="23.875" style="1" customWidth="1"/>
-    <col min="11010" max="11010" width="13.25" style="1" customWidth="1"/>
+    <col min="10999" max="10999" width="14.7109375" style="1" customWidth="1"/>
+    <col min="11000" max="11000" width="13.42578125" style="1" customWidth="1"/>
+    <col min="11001" max="11004" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11005" max="11005" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11006" max="11007" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11008" max="11008" width="14.85546875" style="1" customWidth="1"/>
+    <col min="11009" max="11009" width="23.85546875" style="1" customWidth="1"/>
+    <col min="11010" max="11010" width="13.28515625" style="1" customWidth="1"/>
     <col min="11011" max="11253" width="9" style="1"/>
     <col min="11254" max="11254" width="7" style="1" customWidth="1"/>
-    <col min="11255" max="11255" width="14.75" style="1" customWidth="1"/>
-    <col min="11256" max="11256" width="13.375" style="1" customWidth="1"/>
-    <col min="11257" max="11260" width="9.875" style="1" customWidth="1"/>
-    <col min="11261" max="11261" width="10.75" style="1" customWidth="1"/>
-    <col min="11262" max="11263" width="9.875" style="1" customWidth="1"/>
-    <col min="11264" max="11264" width="14.875" style="1" customWidth="1"/>
-    <col min="11265" max="11265" width="23.875" style="1" customWidth="1"/>
-    <col min="11266" max="11266" width="13.25" style="1" customWidth="1"/>
+    <col min="11255" max="11255" width="14.7109375" style="1" customWidth="1"/>
+    <col min="11256" max="11256" width="13.42578125" style="1" customWidth="1"/>
+    <col min="11257" max="11260" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11261" max="11261" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11262" max="11263" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11264" max="11264" width="14.85546875" style="1" customWidth="1"/>
+    <col min="11265" max="11265" width="23.85546875" style="1" customWidth="1"/>
+    <col min="11266" max="11266" width="13.28515625" style="1" customWidth="1"/>
     <col min="11267" max="11509" width="9" style="1"/>
     <col min="11510" max="11510" width="7" style="1" customWidth="1"/>
-    <col min="11511" max="11511" width="14.75" style="1" customWidth="1"/>
-    <col min="11512" max="11512" width="13.375" style="1" customWidth="1"/>
-    <col min="11513" max="11516" width="9.875" style="1" customWidth="1"/>
-    <col min="11517" max="11517" width="10.75" style="1" customWidth="1"/>
-    <col min="11518" max="11519" width="9.875" style="1" customWidth="1"/>
-    <col min="11520" max="11520" width="14.875" style="1" customWidth="1"/>
-    <col min="11521" max="11521" width="23.875" style="1" customWidth="1"/>
-    <col min="11522" max="11522" width="13.25" style="1" customWidth="1"/>
+    <col min="11511" max="11511" width="14.7109375" style="1" customWidth="1"/>
+    <col min="11512" max="11512" width="13.42578125" style="1" customWidth="1"/>
+    <col min="11513" max="11516" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11517" max="11517" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11518" max="11519" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11520" max="11520" width="14.85546875" style="1" customWidth="1"/>
+    <col min="11521" max="11521" width="23.85546875" style="1" customWidth="1"/>
+    <col min="11522" max="11522" width="13.28515625" style="1" customWidth="1"/>
     <col min="11523" max="11765" width="9" style="1"/>
     <col min="11766" max="11766" width="7" style="1" customWidth="1"/>
-    <col min="11767" max="11767" width="14.75" style="1" customWidth="1"/>
-    <col min="11768" max="11768" width="13.375" style="1" customWidth="1"/>
-    <col min="11769" max="11772" width="9.875" style="1" customWidth="1"/>
-    <col min="11773" max="11773" width="10.75" style="1" customWidth="1"/>
-    <col min="11774" max="11775" width="9.875" style="1" customWidth="1"/>
-    <col min="11776" max="11776" width="14.875" style="1" customWidth="1"/>
-    <col min="11777" max="11777" width="23.875" style="1" customWidth="1"/>
-    <col min="11778" max="11778" width="13.25" style="1" customWidth="1"/>
+    <col min="11767" max="11767" width="14.7109375" style="1" customWidth="1"/>
+    <col min="11768" max="11768" width="13.42578125" style="1" customWidth="1"/>
+    <col min="11769" max="11772" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11773" max="11773" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11774" max="11775" width="9.85546875" style="1" customWidth="1"/>
+    <col min="11776" max="11776" width="14.85546875" style="1" customWidth="1"/>
+    <col min="11777" max="11777" width="23.85546875" style="1" customWidth="1"/>
+    <col min="11778" max="11778" width="13.28515625" style="1" customWidth="1"/>
     <col min="11779" max="12021" width="9" style="1"/>
     <col min="12022" max="12022" width="7" style="1" customWidth="1"/>
-    <col min="12023" max="12023" width="14.75" style="1" customWidth="1"/>
-    <col min="12024" max="12024" width="13.375" style="1" customWidth="1"/>
-    <col min="12025" max="12028" width="9.875" style="1" customWidth="1"/>
-    <col min="12029" max="12029" width="10.75" style="1" customWidth="1"/>
-    <col min="12030" max="12031" width="9.875" style="1" customWidth="1"/>
-    <col min="12032" max="12032" width="14.875" style="1" customWidth="1"/>
-    <col min="12033" max="12033" width="23.875" style="1" customWidth="1"/>
-    <col min="12034" max="12034" width="13.25" style="1" customWidth="1"/>
+    <col min="12023" max="12023" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12024" max="12024" width="13.42578125" style="1" customWidth="1"/>
+    <col min="12025" max="12028" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12029" max="12029" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12030" max="12031" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12032" max="12032" width="14.85546875" style="1" customWidth="1"/>
+    <col min="12033" max="12033" width="23.85546875" style="1" customWidth="1"/>
+    <col min="12034" max="12034" width="13.28515625" style="1" customWidth="1"/>
     <col min="12035" max="12277" width="9" style="1"/>
     <col min="12278" max="12278" width="7" style="1" customWidth="1"/>
-    <col min="12279" max="12279" width="14.75" style="1" customWidth="1"/>
-    <col min="12280" max="12280" width="13.375" style="1" customWidth="1"/>
-    <col min="12281" max="12284" width="9.875" style="1" customWidth="1"/>
-    <col min="12285" max="12285" width="10.75" style="1" customWidth="1"/>
-    <col min="12286" max="12287" width="9.875" style="1" customWidth="1"/>
-    <col min="12288" max="12288" width="14.875" style="1" customWidth="1"/>
-    <col min="12289" max="12289" width="23.875" style="1" customWidth="1"/>
-    <col min="12290" max="12290" width="13.25" style="1" customWidth="1"/>
+    <col min="12279" max="12279" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12280" max="12280" width="13.42578125" style="1" customWidth="1"/>
+    <col min="12281" max="12284" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12285" max="12285" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12286" max="12287" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12288" max="12288" width="14.85546875" style="1" customWidth="1"/>
+    <col min="12289" max="12289" width="23.85546875" style="1" customWidth="1"/>
+    <col min="12290" max="12290" width="13.28515625" style="1" customWidth="1"/>
     <col min="12291" max="12533" width="9" style="1"/>
     <col min="12534" max="12534" width="7" style="1" customWidth="1"/>
-    <col min="12535" max="12535" width="14.75" style="1" customWidth="1"/>
-    <col min="12536" max="12536" width="13.375" style="1" customWidth="1"/>
-    <col min="12537" max="12540" width="9.875" style="1" customWidth="1"/>
-    <col min="12541" max="12541" width="10.75" style="1" customWidth="1"/>
-    <col min="12542" max="12543" width="9.875" style="1" customWidth="1"/>
-    <col min="12544" max="12544" width="14.875" style="1" customWidth="1"/>
-    <col min="12545" max="12545" width="23.875" style="1" customWidth="1"/>
-    <col min="12546" max="12546" width="13.25" style="1" customWidth="1"/>
+    <col min="12535" max="12535" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12536" max="12536" width="13.42578125" style="1" customWidth="1"/>
+    <col min="12537" max="12540" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12541" max="12541" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12542" max="12543" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12544" max="12544" width="14.85546875" style="1" customWidth="1"/>
+    <col min="12545" max="12545" width="23.85546875" style="1" customWidth="1"/>
+    <col min="12546" max="12546" width="13.28515625" style="1" customWidth="1"/>
     <col min="12547" max="12789" width="9" style="1"/>
     <col min="12790" max="12790" width="7" style="1" customWidth="1"/>
-    <col min="12791" max="12791" width="14.75" style="1" customWidth="1"/>
-    <col min="12792" max="12792" width="13.375" style="1" customWidth="1"/>
-    <col min="12793" max="12796" width="9.875" style="1" customWidth="1"/>
-    <col min="12797" max="12797" width="10.75" style="1" customWidth="1"/>
-    <col min="12798" max="12799" width="9.875" style="1" customWidth="1"/>
-    <col min="12800" max="12800" width="14.875" style="1" customWidth="1"/>
-    <col min="12801" max="12801" width="23.875" style="1" customWidth="1"/>
-    <col min="12802" max="12802" width="13.25" style="1" customWidth="1"/>
+    <col min="12791" max="12791" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12792" max="12792" width="13.42578125" style="1" customWidth="1"/>
+    <col min="12793" max="12796" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12797" max="12797" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12798" max="12799" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12800" max="12800" width="14.85546875" style="1" customWidth="1"/>
+    <col min="12801" max="12801" width="23.85546875" style="1" customWidth="1"/>
+    <col min="12802" max="12802" width="13.28515625" style="1" customWidth="1"/>
     <col min="12803" max="13045" width="9" style="1"/>
     <col min="13046" max="13046" width="7" style="1" customWidth="1"/>
-    <col min="13047" max="13047" width="14.75" style="1" customWidth="1"/>
-    <col min="13048" max="13048" width="13.375" style="1" customWidth="1"/>
-    <col min="13049" max="13052" width="9.875" style="1" customWidth="1"/>
-    <col min="13053" max="13053" width="10.75" style="1" customWidth="1"/>
-    <col min="13054" max="13055" width="9.875" style="1" customWidth="1"/>
-    <col min="13056" max="13056" width="14.875" style="1" customWidth="1"/>
-    <col min="13057" max="13057" width="23.875" style="1" customWidth="1"/>
-    <col min="13058" max="13058" width="13.25" style="1" customWidth="1"/>
+    <col min="13047" max="13047" width="14.7109375" style="1" customWidth="1"/>
+    <col min="13048" max="13048" width="13.42578125" style="1" customWidth="1"/>
+    <col min="13049" max="13052" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13053" max="13053" width="10.7109375" style="1" customWidth="1"/>
+    <col min="13054" max="13055" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13056" max="13056" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13057" max="13057" width="23.85546875" style="1" customWidth="1"/>
+    <col min="13058" max="13058" width="13.28515625" style="1" customWidth="1"/>
     <col min="13059" max="13301" width="9" style="1"/>
     <col min="13302" max="13302" width="7" style="1" customWidth="1"/>
-    <col min="13303" max="13303" width="14.75" style="1" customWidth="1"/>
-    <col min="13304" max="13304" width="13.375" style="1" customWidth="1"/>
-    <col min="13305" max="13308" width="9.875" style="1" customWidth="1"/>
-    <col min="13309" max="13309" width="10.75" style="1" customWidth="1"/>
-    <col min="13310" max="13311" width="9.875" style="1" customWidth="1"/>
-    <col min="13312" max="13312" width="14.875" style="1" customWidth="1"/>
-    <col min="13313" max="13313" width="23.875" style="1" customWidth="1"/>
-    <col min="13314" max="13314" width="13.25" style="1" customWidth="1"/>
+    <col min="13303" max="13303" width="14.7109375" style="1" customWidth="1"/>
+    <col min="13304" max="13304" width="13.42578125" style="1" customWidth="1"/>
+    <col min="13305" max="13308" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13309" max="13309" width="10.7109375" style="1" customWidth="1"/>
+    <col min="13310" max="13311" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13312" max="13312" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13313" max="13313" width="23.85546875" style="1" customWidth="1"/>
+    <col min="13314" max="13314" width="13.28515625" style="1" customWidth="1"/>
     <col min="13315" max="13557" width="9" style="1"/>
     <col min="13558" max="13558" width="7" style="1" customWidth="1"/>
-    <col min="13559" max="13559" width="14.75" style="1" customWidth="1"/>
-    <col min="13560" max="13560" width="13.375" style="1" customWidth="1"/>
-    <col min="13561" max="13564" width="9.875" style="1" customWidth="1"/>
-    <col min="13565" max="13565" width="10.75" style="1" customWidth="1"/>
-    <col min="13566" max="13567" width="9.875" style="1" customWidth="1"/>
-    <col min="13568" max="13568" width="14.875" style="1" customWidth="1"/>
-    <col min="13569" max="13569" width="23.875" style="1" customWidth="1"/>
-    <col min="13570" max="13570" width="13.25" style="1" customWidth="1"/>
+    <col min="13559" max="13559" width="14.7109375" style="1" customWidth="1"/>
+    <col min="13560" max="13560" width="13.42578125" style="1" customWidth="1"/>
+    <col min="13561" max="13564" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13565" max="13565" width="10.7109375" style="1" customWidth="1"/>
+    <col min="13566" max="13567" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13568" max="13568" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13569" max="13569" width="23.85546875" style="1" customWidth="1"/>
+    <col min="13570" max="13570" width="13.28515625" style="1" customWidth="1"/>
     <col min="13571" max="13813" width="9" style="1"/>
     <col min="13814" max="13814" width="7" style="1" customWidth="1"/>
-    <col min="13815" max="13815" width="14.75" style="1" customWidth="1"/>
-    <col min="13816" max="13816" width="13.375" style="1" customWidth="1"/>
-    <col min="13817" max="13820" width="9.875" style="1" customWidth="1"/>
-    <col min="13821" max="13821" width="10.75" style="1" customWidth="1"/>
-    <col min="13822" max="13823" width="9.875" style="1" customWidth="1"/>
-    <col min="13824" max="13824" width="14.875" style="1" customWidth="1"/>
-    <col min="13825" max="13825" width="23.875" style="1" customWidth="1"/>
-    <col min="13826" max="13826" width="13.25" style="1" customWidth="1"/>
+    <col min="13815" max="13815" width="14.7109375" style="1" customWidth="1"/>
+    <col min="13816" max="13816" width="13.42578125" style="1" customWidth="1"/>
+    <col min="13817" max="13820" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13821" max="13821" width="10.7109375" style="1" customWidth="1"/>
+    <col min="13822" max="13823" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13824" max="13824" width="14.85546875" style="1" customWidth="1"/>
+    <col min="13825" max="13825" width="23.85546875" style="1" customWidth="1"/>
+    <col min="13826" max="13826" width="13.28515625" style="1" customWidth="1"/>
     <col min="13827" max="14069" width="9" style="1"/>
     <col min="14070" max="14070" width="7" style="1" customWidth="1"/>
-    <col min="14071" max="14071" width="14.75" style="1" customWidth="1"/>
-    <col min="14072" max="14072" width="13.375" style="1" customWidth="1"/>
-    <col min="14073" max="14076" width="9.875" style="1" customWidth="1"/>
-    <col min="14077" max="14077" width="10.75" style="1" customWidth="1"/>
-    <col min="14078" max="14079" width="9.875" style="1" customWidth="1"/>
-    <col min="14080" max="14080" width="14.875" style="1" customWidth="1"/>
-    <col min="14081" max="14081" width="23.875" style="1" customWidth="1"/>
-    <col min="14082" max="14082" width="13.25" style="1" customWidth="1"/>
+    <col min="14071" max="14071" width="14.7109375" style="1" customWidth="1"/>
+    <col min="14072" max="14072" width="13.42578125" style="1" customWidth="1"/>
+    <col min="14073" max="14076" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14077" max="14077" width="10.7109375" style="1" customWidth="1"/>
+    <col min="14078" max="14079" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14080" max="14080" width="14.85546875" style="1" customWidth="1"/>
+    <col min="14081" max="14081" width="23.85546875" style="1" customWidth="1"/>
+    <col min="14082" max="14082" width="13.28515625" style="1" customWidth="1"/>
     <col min="14083" max="14325" width="9" style="1"/>
     <col min="14326" max="14326" width="7" style="1" customWidth="1"/>
-    <col min="14327" max="14327" width="14.75" style="1" customWidth="1"/>
-    <col min="14328" max="14328" width="13.375" style="1" customWidth="1"/>
-    <col min="14329" max="14332" width="9.875" style="1" customWidth="1"/>
-    <col min="14333" max="14333" width="10.75" style="1" customWidth="1"/>
-    <col min="14334" max="14335" width="9.875" style="1" customWidth="1"/>
-    <col min="14336" max="14336" width="14.875" style="1" customWidth="1"/>
-    <col min="14337" max="14337" width="23.875" style="1" customWidth="1"/>
-    <col min="14338" max="14338" width="13.25" style="1" customWidth="1"/>
+    <col min="14327" max="14327" width="14.7109375" style="1" customWidth="1"/>
+    <col min="14328" max="14328" width="13.42578125" style="1" customWidth="1"/>
+    <col min="14329" max="14332" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14333" max="14333" width="10.7109375" style="1" customWidth="1"/>
+    <col min="14334" max="14335" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14336" max="14336" width="14.85546875" style="1" customWidth="1"/>
+    <col min="14337" max="14337" width="23.85546875" style="1" customWidth="1"/>
+    <col min="14338" max="14338" width="13.28515625" style="1" customWidth="1"/>
     <col min="14339" max="14581" width="9" style="1"/>
     <col min="14582" max="14582" width="7" style="1" customWidth="1"/>
-    <col min="14583" max="14583" width="14.75" style="1" customWidth="1"/>
-    <col min="14584" max="14584" width="13.375" style="1" customWidth="1"/>
-    <col min="14585" max="14588" width="9.875" style="1" customWidth="1"/>
-    <col min="14589" max="14589" width="10.75" style="1" customWidth="1"/>
-    <col min="14590" max="14591" width="9.875" style="1" customWidth="1"/>
-    <col min="14592" max="14592" width="14.875" style="1" customWidth="1"/>
-    <col min="14593" max="14593" width="23.875" style="1" customWidth="1"/>
-    <col min="14594" max="14594" width="13.25" style="1" customWidth="1"/>
+    <col min="14583" max="14583" width="14.7109375" style="1" customWidth="1"/>
+    <col min="14584" max="14584" width="13.42578125" style="1" customWidth="1"/>
+    <col min="14585" max="14588" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14589" max="14589" width="10.7109375" style="1" customWidth="1"/>
+    <col min="14590" max="14591" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14592" max="14592" width="14.85546875" style="1" customWidth="1"/>
+    <col min="14593" max="14593" width="23.85546875" style="1" customWidth="1"/>
+    <col min="14594" max="14594" width="13.28515625" style="1" customWidth="1"/>
     <col min="14595" max="14837" width="9" style="1"/>
     <col min="14838" max="14838" width="7" style="1" customWidth="1"/>
-    <col min="14839" max="14839" width="14.75" style="1" customWidth="1"/>
-    <col min="14840" max="14840" width="13.375" style="1" customWidth="1"/>
-    <col min="14841" max="14844" width="9.875" style="1" customWidth="1"/>
-    <col min="14845" max="14845" width="10.75" style="1" customWidth="1"/>
-    <col min="14846" max="14847" width="9.875" style="1" customWidth="1"/>
-    <col min="14848" max="14848" width="14.875" style="1" customWidth="1"/>
-    <col min="14849" max="14849" width="23.875" style="1" customWidth="1"/>
-    <col min="14850" max="14850" width="13.25" style="1" customWidth="1"/>
+    <col min="14839" max="14839" width="14.7109375" style="1" customWidth="1"/>
+    <col min="14840" max="14840" width="13.42578125" style="1" customWidth="1"/>
+    <col min="14841" max="14844" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14845" max="14845" width="10.7109375" style="1" customWidth="1"/>
+    <col min="14846" max="14847" width="9.85546875" style="1" customWidth="1"/>
+    <col min="14848" max="14848" width="14.85546875" style="1" customWidth="1"/>
+    <col min="14849" max="14849" width="23.85546875" style="1" customWidth="1"/>
+    <col min="14850" max="14850" width="13.28515625" style="1" customWidth="1"/>
     <col min="14851" max="15093" width="9" style="1"/>
     <col min="15094" max="15094" width="7" style="1" customWidth="1"/>
-    <col min="15095" max="15095" width="14.75" style="1" customWidth="1"/>
-    <col min="15096" max="15096" width="13.375" style="1" customWidth="1"/>
-    <col min="15097" max="15100" width="9.875" style="1" customWidth="1"/>
-    <col min="15101" max="15101" width="10.75" style="1" customWidth="1"/>
-    <col min="15102" max="15103" width="9.875" style="1" customWidth="1"/>
-    <col min="15104" max="15104" width="14.875" style="1" customWidth="1"/>
-    <col min="15105" max="15105" width="23.875" style="1" customWidth="1"/>
-    <col min="15106" max="15106" width="13.25" style="1" customWidth="1"/>
+    <col min="15095" max="15095" width="14.7109375" style="1" customWidth="1"/>
+    <col min="15096" max="15096" width="13.42578125" style="1" customWidth="1"/>
+    <col min="15097" max="15100" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15101" max="15101" width="10.7109375" style="1" customWidth="1"/>
+    <col min="15102" max="15103" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15104" max="15104" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15105" max="15105" width="23.85546875" style="1" customWidth="1"/>
+    <col min="15106" max="15106" width="13.28515625" style="1" customWidth="1"/>
     <col min="15107" max="15349" width="9" style="1"/>
     <col min="15350" max="15350" width="7" style="1" customWidth="1"/>
-    <col min="15351" max="15351" width="14.75" style="1" customWidth="1"/>
-    <col min="15352" max="15352" width="13.375" style="1" customWidth="1"/>
-    <col min="15353" max="15356" width="9.875" style="1" customWidth="1"/>
-    <col min="15357" max="15357" width="10.75" style="1" customWidth="1"/>
-    <col min="15358" max="15359" width="9.875" style="1" customWidth="1"/>
-    <col min="15360" max="15360" width="14.875" style="1" customWidth="1"/>
-    <col min="15361" max="15361" width="23.875" style="1" customWidth="1"/>
-    <col min="15362" max="15362" width="13.25" style="1" customWidth="1"/>
+    <col min="15351" max="15351" width="14.7109375" style="1" customWidth="1"/>
+    <col min="15352" max="15352" width="13.42578125" style="1" customWidth="1"/>
+    <col min="15353" max="15356" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15357" max="15357" width="10.7109375" style="1" customWidth="1"/>
+    <col min="15358" max="15359" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15360" max="15360" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15361" max="15361" width="23.85546875" style="1" customWidth="1"/>
+    <col min="15362" max="15362" width="13.28515625" style="1" customWidth="1"/>
     <col min="15363" max="15605" width="9" style="1"/>
     <col min="15606" max="15606" width="7" style="1" customWidth="1"/>
-    <col min="15607" max="15607" width="14.75" style="1" customWidth="1"/>
-    <col min="15608" max="15608" width="13.375" style="1" customWidth="1"/>
-    <col min="15609" max="15612" width="9.875" style="1" customWidth="1"/>
-    <col min="15613" max="15613" width="10.75" style="1" customWidth="1"/>
-    <col min="15614" max="15615" width="9.875" style="1" customWidth="1"/>
-    <col min="15616" max="15616" width="14.875" style="1" customWidth="1"/>
-    <col min="15617" max="15617" width="23.875" style="1" customWidth="1"/>
-    <col min="15618" max="15618" width="13.25" style="1" customWidth="1"/>
+    <col min="15607" max="15607" width="14.7109375" style="1" customWidth="1"/>
+    <col min="15608" max="15608" width="13.42578125" style="1" customWidth="1"/>
+    <col min="15609" max="15612" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15613" max="15613" width="10.7109375" style="1" customWidth="1"/>
+    <col min="15614" max="15615" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15616" max="15616" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15617" max="15617" width="23.85546875" style="1" customWidth="1"/>
+    <col min="15618" max="15618" width="13.28515625" style="1" customWidth="1"/>
     <col min="15619" max="15861" width="9" style="1"/>
     <col min="15862" max="15862" width="7" style="1" customWidth="1"/>
-    <col min="15863" max="15863" width="14.75" style="1" customWidth="1"/>
-    <col min="15864" max="15864" width="13.375" style="1" customWidth="1"/>
-    <col min="15865" max="15868" width="9.875" style="1" customWidth="1"/>
-    <col min="15869" max="15869" width="10.75" style="1" customWidth="1"/>
-    <col min="15870" max="15871" width="9.875" style="1" customWidth="1"/>
-    <col min="15872" max="15872" width="14.875" style="1" customWidth="1"/>
-    <col min="15873" max="15873" width="23.875" style="1" customWidth="1"/>
-    <col min="15874" max="15874" width="13.25" style="1" customWidth="1"/>
+    <col min="15863" max="15863" width="14.7109375" style="1" customWidth="1"/>
+    <col min="15864" max="15864" width="13.42578125" style="1" customWidth="1"/>
+    <col min="15865" max="15868" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15869" max="15869" width="10.7109375" style="1" customWidth="1"/>
+    <col min="15870" max="15871" width="9.85546875" style="1" customWidth="1"/>
+    <col min="15872" max="15872" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15873" max="15873" width="23.85546875" style="1" customWidth="1"/>
+    <col min="15874" max="15874" width="13.28515625" style="1" customWidth="1"/>
     <col min="15875" max="16117" width="9" style="1"/>
     <col min="16118" max="16118" width="7" style="1" customWidth="1"/>
-    <col min="16119" max="16119" width="14.75" style="1" customWidth="1"/>
-    <col min="16120" max="16120" width="13.375" style="1" customWidth="1"/>
-    <col min="16121" max="16124" width="9.875" style="1" customWidth="1"/>
-    <col min="16125" max="16125" width="10.75" style="1" customWidth="1"/>
-    <col min="16126" max="16127" width="9.875" style="1" customWidth="1"/>
-    <col min="16128" max="16128" width="14.875" style="1" customWidth="1"/>
-    <col min="16129" max="16129" width="23.875" style="1" customWidth="1"/>
-    <col min="16130" max="16130" width="13.25" style="1" customWidth="1"/>
+    <col min="16119" max="16119" width="14.7109375" style="1" customWidth="1"/>
+    <col min="16120" max="16120" width="13.42578125" style="1" customWidth="1"/>
+    <col min="16121" max="16124" width="9.85546875" style="1" customWidth="1"/>
+    <col min="16125" max="16125" width="10.7109375" style="1" customWidth="1"/>
+    <col min="16126" max="16127" width="9.85546875" style="1" customWidth="1"/>
+    <col min="16128" max="16128" width="14.85546875" style="1" customWidth="1"/>
+    <col min="16129" max="16129" width="23.85546875" style="1" customWidth="1"/>
+    <col min="16130" max="16130" width="13.28515625" style="1" customWidth="1"/>
     <col min="16131" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="25" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
     </row>
-    <row r="2" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="25" t="s">
+    <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
     </row>
-    <row r="3" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="17"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="15"/>
-      <c r="AC3" s="15"/>
-      <c r="AD3" s="15"/>
-      <c r="AE3" s="15"/>
-      <c r="AF3" s="15"/>
-      <c r="AG3" s="15"/>
+    <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
     </row>
-    <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
     </row>
-    <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="11">
+    <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>2</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>3</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>4</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>6</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>7</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>8</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>9</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>10</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>11</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>12</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>13</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="10">
         <v>14</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="10">
         <v>15</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="10">
         <v>16</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="10">
         <v>17</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="10">
         <v>18</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="10">
         <v>19</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="10">
         <v>20</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="10">
         <v>21</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="10">
         <v>22</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="10">
         <v>23</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="Z5" s="10">
         <v>24</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AA5" s="10">
         <v>25</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="10">
         <v>26</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AC5" s="10">
         <v>27</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AD5" s="10">
         <v>28</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="10">
         <v>29</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AF5" s="10">
         <v>30</v>
       </c>
-      <c r="AG5" s="11">
+      <c r="AG5" s="10">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="12">
+    <row r="6" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+      <c r="AG6" s="12"/>
     </row>
-    <row r="7" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="9">
+    <row r="7" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
     </row>
-    <row r="8" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="9">
+    <row r="8" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
     </row>
-    <row r="9" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="9">
+    <row r="9" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="12"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="12"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="12"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
     </row>
-    <row r="10" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="8">
+    <row r="10" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="7">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
     </row>
     <row r="11" spans="1:33" ht="22.5" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
     </row>
     <row r="12" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B12" s="5"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="23"/>
       <c r="D12" s="23"/>
       <c r="E12" s="23"/>
@@ -2007,41 +2010,41 @@
       <c r="AG12" s="23"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B13" s="5"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="31"/>
-      <c r="AF13" s="31"/>
-      <c r="AG13" s="31"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B14" s="5"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
@@ -2075,103 +2078,101 @@
       <c r="AG14" s="23"/>
     </row>
     <row r="15" spans="1:33" ht="19.5" customHeight="1">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="338.25" customHeight="1">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="34"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="34"/>
-      <c r="AC16" s="34"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="34"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
     </row>
-    <row r="17" spans="3:33" ht="21">
-      <c r="AA17" s="4"/>
-      <c r="AB17" s="4"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="33"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="33"/>
+    <row r="17" spans="3:33" ht="21" customHeight="1">
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="34"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
     </row>
     <row r="18" spans="3:33" ht="29.25" customHeight="1">
-      <c r="AC18" s="32" t="s">
+      <c r="AB18" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
+      <c r="AC18" s="21"/>
+      <c r="AD18" s="21"/>
+      <c r="AE18" s="21"/>
+      <c r="AF18" s="21"/>
+      <c r="AG18" s="21"/>
     </row>
     <row r="19" spans="3:33" ht="14.25" customHeight="1">
-      <c r="C19" s="3"/>
-      <c r="AG19" s="2" t="s">
+      <c r="C19" s="2"/>
+      <c r="AB19" s="33" t="s">
         <v>0</v>
       </c>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="AC18:AG18"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AC17:AG17"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
+  <mergeCells count="72">
+    <mergeCell ref="AB18:AG18"/>
+    <mergeCell ref="AB19:AG19"/>
+    <mergeCell ref="AB17:AG17"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="Q11:Q12"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="P13:P14"/>
@@ -2188,32 +2189,41 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="B16:AG16"/>
+    <mergeCell ref="Q13:Q14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="76" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="78" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FM-MN-07_BAND SAW-02.xlsx
+++ b/FM-MN-07_BAND SAW-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From Iso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBBC4D9-0437-4426-B976-A12DEB6DE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02B6585-02B6-4A56-82F0-CE3388AD5698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{DE5370CA-647C-48FC-A6D6-FC5AAC313DA8}"/>
   </bookViews>
@@ -405,43 +405,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1497,80 +1497,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="27" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="27" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1608,49 +1608,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="31"/>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="29"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="10">
         <v>1</v>
       </c>
@@ -1943,139 +1943,139 @@
     <row r="11" spans="1:33" ht="22.5" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="23"/>
+      <c r="AD11" s="23"/>
+      <c r="AE11" s="23"/>
+      <c r="AF11" s="23"/>
+      <c r="AG11" s="23"/>
     </row>
     <row r="12" spans="1:33" ht="22.5" customHeight="1">
       <c r="B12" s="4"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="23"/>
-      <c r="AD12" s="23"/>
-      <c r="AE12" s="23"/>
-      <c r="AF12" s="23"/>
-      <c r="AG12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="B13" s="4"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="32"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="4"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
     </row>
     <row r="15" spans="1:33" ht="19.5" customHeight="1">
       <c r="B15" s="20" t="s">
@@ -2083,38 +2083,38 @@
       </c>
     </row>
     <row r="16" spans="1:33" ht="338.25" customHeight="1">
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="33"/>
     </row>
     <row r="17" spans="3:33" ht="21" customHeight="1">
       <c r="AA17" s="3"/>
@@ -2137,65 +2137,23 @@
     </row>
     <row r="19" spans="3:33" ht="14.25" customHeight="1">
       <c r="C19" s="2"/>
-      <c r="AB19" s="33" t="s">
+      <c r="AB19" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="33"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="33"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="AB18:AG18"/>
-    <mergeCell ref="AB19:AG19"/>
-    <mergeCell ref="AB17:AG17"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="B16:AG16"/>
+    <mergeCell ref="Q13:Q14"/>
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AE11:AE12"/>
     <mergeCell ref="AF11:AF12"/>
@@ -2207,19 +2165,61 @@
     <mergeCell ref="X11:X12"/>
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
     <mergeCell ref="X13:X14"/>
     <mergeCell ref="Y13:Y14"/>
     <mergeCell ref="Z13:Z14"/>
     <mergeCell ref="AA13:AA14"/>
     <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AB18:AG18"/>
+    <mergeCell ref="AB19:AG19"/>
+    <mergeCell ref="AB17:AG17"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
